--- a/manuscript_material/source_data/Source_Data_ED_Fig2.xlsx
+++ b/manuscript_material/source_data/Source_Data_ED_Fig2.xlsx
@@ -423,7 +423,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -433,12 +433,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>triplicates</t>
+          <t>replicate_sets</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>mean_jaccard</t>
+          <t>tool_set_similarity</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -613,17 +613,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>replicate</t>
+          <t>replicate_run</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>scored_correct</t>
         </is>
       </c>
     </row>
@@ -1284,17 +1284,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>replicate</t>
+          <t>replicate_run</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>scored_correct</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>verifier</t>
+          <t>verifier_mode</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2564,7 +2564,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Galaxy output, GPT-5.6 Luna replicate 1 (BWA-MEM)</t>
+          <t>Galaxy output, GPT-5.6 Luna replicate run 1 (BWA-MEM)</t>
         </is>
       </c>
       <c r="B2" t="n">
